--- a/docsrc/performance.xlsx
+++ b/docsrc/performance.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mueller/data/bau/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mueller/data/bau/docsrc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C768EC-CE2E-1049-828C-8374B17E1E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246D0475-AB53-1140-9363-CA301284BF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="500" windowWidth="34040" windowHeight="17500" activeTab="1" xr2:uid="{8BA8907E-A4D7-9D46-8614-8210467CB087}"/>
+    <workbookView xWindow="4320" yWindow="500" windowWidth="34040" windowHeight="17500" activeTab="2" xr2:uid="{8BA8907E-A4D7-9D46-8614-8210467CB087}"/>
   </bookViews>
   <sheets>
     <sheet name="Performance" sheetId="1" r:id="rId1"/>
     <sheet name="Concise" sheetId="2" r:id="rId2"/>
-    <sheet name="signal" sheetId="3" r:id="rId3"/>
+    <sheet name="Memory" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t>Benchmark</t>
   </si>
@@ -106,369 +106,6 @@
     <t>8.25 seconds per million nodes</t>
   </si>
   <si>
-    <t>  </t>
-  </si>
-  <si>
-    <t> </t>
-  </si>
-  <si>
-    <t>1  </t>
-  </si>
-  <si>
-    <t>SIGHUP  </t>
-  </si>
-  <si>
-    <t>terminate process </t>
-  </si>
-  <si>
-    <t>terminal line hangup</t>
-  </si>
-  <si>
-    <t>2  </t>
-  </si>
-  <si>
-    <t>SIGINT  </t>
-  </si>
-  <si>
-    <t>interrupt program</t>
-  </si>
-  <si>
-    <t>3  </t>
-  </si>
-  <si>
-    <t>SIGQUIT </t>
-  </si>
-  <si>
-    <t>create core image </t>
-  </si>
-  <si>
-    <t>quit program</t>
-  </si>
-  <si>
-    <t>4  </t>
-  </si>
-  <si>
-    <t>SIGILL  </t>
-  </si>
-  <si>
-    <t>illegal instruction</t>
-  </si>
-  <si>
-    <t>5  </t>
-  </si>
-  <si>
-    <t>SIGTRAP </t>
-  </si>
-  <si>
-    <t>trace trap</t>
-  </si>
-  <si>
-    <t>6  </t>
-  </si>
-  <si>
-    <t>SIGABRT </t>
-  </si>
-  <si>
-    <t>abort program (formerly SIGIOT)</t>
-  </si>
-  <si>
-    <t>7  </t>
-  </si>
-  <si>
-    <t>SIGEMT  </t>
-  </si>
-  <si>
-    <t>emulate instruction executed</t>
-  </si>
-  <si>
-    <t>8  </t>
-  </si>
-  <si>
-    <t>SIGFPE  </t>
-  </si>
-  <si>
-    <t>floating-point exception</t>
-  </si>
-  <si>
-    <t>9  </t>
-  </si>
-  <si>
-    <t>SIGKILL </t>
-  </si>
-  <si>
-    <t>kill program</t>
-  </si>
-  <si>
-    <t>10 </t>
-  </si>
-  <si>
-    <t>SIGBUS  </t>
-  </si>
-  <si>
-    <t>bus error</t>
-  </si>
-  <si>
-    <t>11 </t>
-  </si>
-  <si>
-    <t>SIGSEGV </t>
-  </si>
-  <si>
-    <t>segmentation violation</t>
-  </si>
-  <si>
-    <t>12 </t>
-  </si>
-  <si>
-    <t>SIGSYS  </t>
-  </si>
-  <si>
-    <t>non-existent system call invoked</t>
-  </si>
-  <si>
-    <t>13 </t>
-  </si>
-  <si>
-    <t>SIGPIPE </t>
-  </si>
-  <si>
-    <t>write on a pipe with no reader</t>
-  </si>
-  <si>
-    <t>14 </t>
-  </si>
-  <si>
-    <t>SIGALRM </t>
-  </si>
-  <si>
-    <t>real-time timer expired</t>
-  </si>
-  <si>
-    <t>15 </t>
-  </si>
-  <si>
-    <t>SIGTERM </t>
-  </si>
-  <si>
-    <t>software termination signal</t>
-  </si>
-  <si>
-    <t>16 </t>
-  </si>
-  <si>
-    <t>SIGURG  </t>
-  </si>
-  <si>
-    <t>discard signal    </t>
-  </si>
-  <si>
-    <t>urgent condition present on socket</t>
-  </si>
-  <si>
-    <t>17 </t>
-  </si>
-  <si>
-    <t>SIGSTOP </t>
-  </si>
-  <si>
-    <t>stop process      </t>
-  </si>
-  <si>
-    <t>stop (cannot be caught or ignored)</t>
-  </si>
-  <si>
-    <t>18 </t>
-  </si>
-  <si>
-    <t>SIGTSTP </t>
-  </si>
-  <si>
-    <t>stop signal generated from keyboard</t>
-  </si>
-  <si>
-    <t>19 </t>
-  </si>
-  <si>
-    <t>SIGCONT </t>
-  </si>
-  <si>
-    <t>continue after stop</t>
-  </si>
-  <si>
-    <t>20 </t>
-  </si>
-  <si>
-    <t>SIGCHLD </t>
-  </si>
-  <si>
-    <t>child status has changed</t>
-  </si>
-  <si>
-    <t>21 </t>
-  </si>
-  <si>
-    <t>SIGTTIN </t>
-  </si>
-  <si>
-    <t>background read attempted from control terminal</t>
-  </si>
-  <si>
-    <t>22 </t>
-  </si>
-  <si>
-    <t>SIGTTOU </t>
-  </si>
-  <si>
-    <t>background write attempted to control terminal</t>
-  </si>
-  <si>
-    <t>23 </t>
-  </si>
-  <si>
-    <t>SIGIO   </t>
-  </si>
-  <si>
-    <t>I/O is possible on a descriptor (see fcntl(2))</t>
-  </si>
-  <si>
-    <t>24 </t>
-  </si>
-  <si>
-    <t>SIGXCPU </t>
-  </si>
-  <si>
-    <t>cpu time limit exceeded (see setrlimit(2))</t>
-  </si>
-  <si>
-    <t>25 </t>
-  </si>
-  <si>
-    <t>SIGXFSZ </t>
-  </si>
-  <si>
-    <t>file size limit exceeded (see setrlimit(2))</t>
-  </si>
-  <si>
-    <t>26 </t>
-  </si>
-  <si>
-    <t>virtual time alarm (see setitimer(2))</t>
-  </si>
-  <si>
-    <t>27 </t>
-  </si>
-  <si>
-    <t>SIGPROF </t>
-  </si>
-  <si>
-    <t>profiling timer alarm (see setitimer(2))</t>
-  </si>
-  <si>
-    <t>28 </t>
-  </si>
-  <si>
-    <t>SIGWINCH</t>
-  </si>
-  <si>
-    <t>Window size change</t>
-  </si>
-  <si>
-    <t>29 </t>
-  </si>
-  <si>
-    <t>SIGINFO </t>
-  </si>
-  <si>
-    <t>status request from keyboard</t>
-  </si>
-  <si>
-    <t>30 </t>
-  </si>
-  <si>
-    <t>SIGUSR1 </t>
-  </si>
-  <si>
-    <t>User defined signal 1</t>
-  </si>
-  <si>
-    <t>31 </t>
-  </si>
-  <si>
-    <t>SIGUSR2 </t>
-  </si>
-  <si>
-    <t>User defined signal 2</t>
-  </si>
-  <si>
-    <t>SIGVTALRM</t>
-  </si>
-  <si>
-    <t>default action</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>signal</t>
-  </si>
-  <si>
-    <t>hang up</t>
-  </si>
-  <si>
-    <t>interrupt</t>
-  </si>
-  <si>
-    <t>quit</t>
-  </si>
-  <si>
-    <t>illegal</t>
-  </si>
-  <si>
-    <t>trap</t>
-  </si>
-  <si>
-    <t>abort</t>
-  </si>
-  <si>
-    <t>emulate</t>
-  </si>
-  <si>
-    <t>kill</t>
-  </si>
-  <si>
-    <t>floating point exception</t>
-  </si>
-  <si>
-    <t>non-existent syscall</t>
-  </si>
-  <si>
-    <t>pipe without reader</t>
-  </si>
-  <si>
-    <t>timer</t>
-  </si>
-  <si>
-    <t>terminate</t>
-  </si>
-  <si>
-    <t>urgent</t>
-  </si>
-  <si>
-    <t>stop</t>
-  </si>
-  <si>
-    <t>continue</t>
-  </si>
-  <si>
-    <t>child</t>
-  </si>
-  <si>
-    <t>window size changed</t>
-  </si>
-  <si>
     <t>Underscore</t>
   </si>
   <si>
@@ -479,6 +116,9 @@
   </si>
   <si>
     <t>Zig</t>
+  </si>
+  <si>
+    <t>Stop-the-world GC pause in ms</t>
   </si>
 </sst>
 </file>
@@ -3313,6 +2953,406 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="0" baseline="0"/>
+              <a:t>Stop-the-world GC pause </a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="en-US" b="1" i="0" baseline="0"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="0" baseline="0"/>
+              <a:t>in ms (smaller is better)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Memory!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Stop-the-world GC pause in ms</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Memory!$B$3:$H$3</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Bau</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Go</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Java</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>PyPy</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Python</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Rust</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Swift</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Memory!$B$4:$H$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BCFC-AC40-9084-8D2BD57D84B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="922637663"/>
+        <c:axId val="922640271"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="922637663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="922640271"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="922640271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="922637663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3433,6 +3473,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
@@ -4444,6 +4524,511 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5224,6 +5809,47 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>412750</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08A041E7-4264-E85A-D1D1-11BBA8FE36C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5576,7 +6202,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>10</v>
@@ -5588,10 +6214,10 @@
         <v>20</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>11</v>
@@ -5994,7 +6620,7 @@
         <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>12</v>
@@ -6135,7 +6761,7 @@
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>252</v>
@@ -6277,7 +6903,7 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>306</v>
@@ -6703,7 +7329,7 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>376</v>
@@ -6967,834 +7593,149 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBCE9842-6C14-0245-8092-DD3DC9C4F639}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A2:H29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="3"/>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="C4" s="1">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="str">
-        <f>"    " &amp; D2 &amp; "  # " &amp;J2</f>
-        <v xml:space="preserve">    SIGHUP    # hang up</v>
-      </c>
-      <c r="J2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="str">
-        <f t="shared" ref="G3:G32" si="0">"    " &amp; D3 &amp; "  # " &amp;J3</f>
-        <v xml:space="preserve">    SIGINT    # interrupt</v>
-      </c>
-      <c r="J3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGQUIT   # quit</v>
-      </c>
-      <c r="J4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGILL    # illegal</v>
-      </c>
-      <c r="J5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGTRAP   # trap</v>
-      </c>
-      <c r="J6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGABRT   # abort</v>
-      </c>
-      <c r="J7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGEMT    # emulate</v>
-      </c>
-      <c r="J8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGFPE    # floating point exception</v>
-      </c>
-      <c r="J9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGKILL   # kill</v>
-      </c>
-      <c r="J10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGBUS    # bus error</v>
-      </c>
-      <c r="J11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGSEGV   # segmentation violation</v>
-      </c>
-      <c r="J12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGSYS    # non-existent syscall</v>
-      </c>
-      <c r="J13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGPIPE   # pipe without reader</v>
-      </c>
-      <c r="J14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGALRM   # timer</v>
-      </c>
-      <c r="J15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGTERM   # terminate</v>
-      </c>
-      <c r="J16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGURG    # urgent</v>
-      </c>
-      <c r="J17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGSTOP   # stop</v>
-      </c>
-      <c r="J18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGTSTP   # </v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGCONT   # continue</v>
-      </c>
-      <c r="J20" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGCHLD   # child</v>
-      </c>
-      <c r="J21" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGTTIN   # </v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGTTOU   # </v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" t="s">
-        <v>96</v>
-      </c>
-      <c r="G24" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGIO     # </v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" t="s">
-        <v>99</v>
-      </c>
-      <c r="G25" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGXCPU   # </v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G26" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGXFSZ   # </v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGVTALRM  # </v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" t="s">
-        <v>107</v>
-      </c>
-      <c r="G28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGPROF   # </v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" t="s">
-        <v>110</v>
-      </c>
-      <c r="G29" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGWINCH  # window size changed</v>
-      </c>
-      <c r="J29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>112</v>
-      </c>
-      <c r="E30" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGINFO   # </v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" t="s">
-        <v>116</v>
-      </c>
-      <c r="G31" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGUSR1   # </v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" t="s">
-        <v>119</v>
-      </c>
-      <c r="G32" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    SIGUSR2   # </v>
-      </c>
+      <c r="D4" s="1">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1">
+        <v>12.9</v>
+      </c>
+      <c r="F4" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docsrc/performance.xlsx
+++ b/docsrc/performance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mueller/data/bau/docsrc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246D0475-AB53-1140-9363-CA301284BF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5501AD02-AC3A-8A41-A8C2-8121B33635ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="500" windowWidth="34040" windowHeight="17500" activeTab="2" xr2:uid="{8BA8907E-A4D7-9D46-8614-8210467CB087}"/>
+    <workbookView xWindow="4320" yWindow="500" windowWidth="34040" windowHeight="17500" xr2:uid="{8BA8907E-A4D7-9D46-8614-8210467CB087}"/>
   </bookViews>
   <sheets>
     <sheet name="Performance" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
   <si>
     <t>Benchmark</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>Stop-the-world GC pause in ms</t>
+  </si>
+  <si>
+    <t>Nbody</t>
   </si>
 </sst>
 </file>
@@ -817,6 +820,113 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-9C4A-2A4F-8C3D-1F740C03D694}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Performance!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nbody</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Performance!$C$4:$L$4</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Bau</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>C</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Go</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Java</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Nim</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>PyPy</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Rust</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Swift</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Vlang</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Zig</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Performance!$C$10:$L$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C3FE-7147-B843-EA0864A67C7F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1151,16 +1261,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>222</c:v>
+                  <c:v>354</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5410</c:v>
+                  <c:v>9349</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2086</c:v>
+                  <c:v>3496</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2595</c:v>
+                  <c:v>4572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1222,16 +1332,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>227</c:v>
+                  <c:v>354</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5396</c:v>
+                  <c:v>9324</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2063</c:v>
+                  <c:v>3506</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2698</c:v>
+                  <c:v>4668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1293,16 +1403,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>252</c:v>
+                  <c:v>381</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6096</c:v>
+                  <c:v>10311</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2351</c:v>
+                  <c:v>3808</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3068</c:v>
+                  <c:v>5252</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1364,16 +1474,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>283</c:v>
+                  <c:v>433</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6571</c:v>
+                  <c:v>10997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2542</c:v>
+                  <c:v>4114</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3195</c:v>
+                  <c:v>5416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1435,16 +1545,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>306</c:v>
+                  <c:v>456</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6726</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2734</c:v>
+                  <c:v>4259</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3028</c:v>
+                  <c:v>4993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1506,16 +1616,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>277</c:v>
+                  <c:v>436</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6953</c:v>
+                  <c:v>11901</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2590</c:v>
+                  <c:v>4717</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3501</c:v>
+                  <c:v>5676</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1579,16 +1689,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>334</c:v>
+                  <c:v>483</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7037</c:v>
+                  <c:v>11208</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2764</c:v>
+                  <c:v>4306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3217</c:v>
+                  <c:v>5230</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1652,16 +1762,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>306</c:v>
+                  <c:v>455</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7268</c:v>
+                  <c:v>11821</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2604</c:v>
+                  <c:v>4186</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3477</c:v>
+                  <c:v>5709</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1725,16 +1835,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>278</c:v>
+                  <c:v>430</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7928</c:v>
+                  <c:v>13126</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3322</c:v>
+                  <c:v>5449</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3601</c:v>
+                  <c:v>5960</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1798,16 +1908,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>340</c:v>
+                  <c:v>491</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8314</c:v>
+                  <c:v>12778</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3311</c:v>
+                  <c:v>4885</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3693</c:v>
+                  <c:v>5854</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1871,16 +1981,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>376</c:v>
+                  <c:v>538</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10209</c:v>
+                  <c:v>15363</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3526</c:v>
+                  <c:v>5306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5011</c:v>
+                  <c:v>7495</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2258,34 +2368,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0225225225225225</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1351351351351351</c:v>
+                  <c:v>1.076271186440678</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2747747747747749</c:v>
+                  <c:v>1.2231638418079096</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3783783783783783</c:v>
+                  <c:v>1.2881355932203389</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.2477477477477477</c:v>
+                  <c:v>1.231638418079096</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5045045045045045</c:v>
+                  <c:v>1.3644067796610169</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3783783783783783</c:v>
+                  <c:v>1.2853107344632768</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.2522522522522523</c:v>
+                  <c:v>1.2146892655367232</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5315315315315314</c:v>
+                  <c:v>1.3870056497175141</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.6936936936936937</c:v>
+                  <c:v>1.5197740112994351</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2371,34 +2481,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.99741219963031424</c:v>
+                  <c:v>0.99732591721039687</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1268022181146025</c:v>
+                  <c:v>1.1028987057439299</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2146025878003697</c:v>
+                  <c:v>1.1762755374906408</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.2432532347504621</c:v>
+                  <c:v>1.1552037651085678</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.2852125693160812</c:v>
+                  <c:v>1.2729703711626912</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.3007393715341959</c:v>
+                  <c:v>1.1988447962348916</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3434380776340111</c:v>
+                  <c:v>1.264413306235961</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.4654343807763401</c:v>
+                  <c:v>1.4040004278532463</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5367837338262476</c:v>
+                  <c:v>1.3667771954219703</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.8870609981515711</c:v>
+                  <c:v>1.6432773558669378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2484,34 +2594,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98897411313518691</c:v>
+                  <c:v>1.0028604118993134</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1270373921380632</c:v>
+                  <c:v>1.0892448512585813</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2186001917545541</c:v>
+                  <c:v>1.1767734553775744</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3106423777564717</c:v>
+                  <c:v>1.2182494279176201</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.2416107382550334</c:v>
+                  <c:v>1.3492562929061784</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.3250239693192714</c:v>
+                  <c:v>1.2316933638443937</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.2483221476510067</c:v>
+                  <c:v>1.1973684210526316</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.592521572387344</c:v>
+                  <c:v>1.5586384439359269</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.587248322147651</c:v>
+                  <c:v>1.3973112128146452</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.6903163950143816</c:v>
+                  <c:v>1.5177345537757436</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2597,34 +2707,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0396917148362235</c:v>
+                  <c:v>1.0209973753280841</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1822736030828516</c:v>
+                  <c:v>1.1487314085739282</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.23121387283237</c:v>
+                  <c:v>1.1846019247594051</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.166859344894027</c:v>
+                  <c:v>1.0920822397200349</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.3491329479768785</c:v>
+                  <c:v>1.2414698162729658</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2396917148362234</c:v>
+                  <c:v>1.1439195100612425</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3398843930635838</c:v>
+                  <c:v>1.2486876640419948</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.3876685934489403</c:v>
+                  <c:v>1.3035870516185477</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.4231213872832371</c:v>
+                  <c:v>1.2804024496937882</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.9310211946050098</c:v>
+                  <c:v>1.639326334208224</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2707,37 +2817,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0.99999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.93519882179675995</c:v>
+                  <c:v>0.93305439330543927</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99263622974963184</c:v>
+                  <c:v>1.0150627615062762</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2268041237113403</c:v>
+                  <c:v>1.1983263598326359</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3019145802650958</c:v>
+                  <c:v>1.1983263598326359</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.2739322533136965</c:v>
+                  <c:v>1.2359832635983263</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5022091310751104</c:v>
+                  <c:v>1.3615062761506276</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6583210603829159</c:v>
+                  <c:v>1.5313807531380752</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.4830633284241532</c:v>
+                  <c:v>1.4100418410041839</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.8335787923416789</c:v>
+                  <c:v>1.6200836820083682</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.4491899852724592</c:v>
+                  <c:v>2.1037656903765689</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5539,13 +5649,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>59947</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>6846</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>245270</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>235229</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5605,13 +5715,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>171621</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>96109</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>36727</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>203372</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5641,13 +5751,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>77229</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>137298</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>231690</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>42905</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5691,13 +5801,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>66588</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>15104</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>221049</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>186725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -6175,7 +6285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{430266A2-5A9C-AA42-B61E-0693631C31C7}">
-  <dimension ref="B4:O23"/>
+  <dimension ref="B4:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
@@ -6261,7 +6371,7 @@
         <v>67</v>
       </c>
       <c r="O5">
-        <f t="shared" ref="O5:O10" si="0">N5/H5</f>
+        <f t="shared" ref="O5:O11" si="0">N5/H5</f>
         <v>12.181818181818182</v>
       </c>
     </row>
@@ -6434,73 +6544,106 @@
       </c>
     </row>
     <row r="10" spans="2:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C10" s="1">
-        <f t="shared" ref="C10:I10" si="1">SUM(C5:C9)</f>
-        <v>9.3000000000000007</v>
+        <v>1.5</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="1"/>
-        <v>8.2000000000000011</v>
+        <v>1.4</v>
       </c>
       <c r="E10" s="1">
-        <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>1.9</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="1"/>
-        <v>33</v>
+        <v>1.6</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="1"/>
-        <v>30.599999999999998</v>
+        <v>10.4</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="1"/>
-        <v>9.6999999999999993</v>
+        <v>1.7</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" ref="J10" si="2">SUM(J5:J9)</f>
-        <v>28.7</v>
+        <v>1.7</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" ref="K10" si="3">SUM(K5:K9)</f>
-        <v>12.3</v>
+        <v>1.6</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:N10" si="4">SUM(L5:L9)</f>
-        <v>19.8</v>
+        <v>1.5</v>
       </c>
       <c r="N10" s="1">
-        <f t="shared" si="4"/>
-        <v>392.8</v>
+        <v>167</v>
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>12.836601307189543</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+        <v>16.057692307692307</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="21" x14ac:dyDescent="0.25">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1">
+        <f t="shared" ref="C11:L11" si="1">SUM(C5:C10)</f>
+        <v>10.8</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="1"/>
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="1"/>
+        <v>12.4</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="1"/>
+        <v>34.6</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="1"/>
+        <v>11.399999999999999</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="1"/>
+        <v>30.4</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="1"/>
+        <v>13.9</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="1"/>
+        <v>21.3</v>
+      </c>
+      <c r="N11" s="1">
+        <f>SUM(N5:N10)</f>
+        <v>559.79999999999995</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>13.653658536585365</v>
+      </c>
     </row>
     <row r="13" spans="2:15" ht="21" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" spans="2:15" ht="21" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
@@ -6537,52 +6680,61 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="K17" s="5">
+    </row>
+    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="K18" s="5">
         <v>0.42202546296296295</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="K18" s="5">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="K19" s="5">
         <v>0.4258912037037037</v>
       </c>
-      <c r="L18" s="5">
-        <f>K18-K17</f>
+      <c r="L19" s="5">
+        <f>K19-K18</f>
         <v>3.8657407407407529E-3</v>
       </c>
-      <c r="M18">
+      <c r="M19">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="M19">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M20">
         <f>60*5+30</f>
         <v>330</v>
       </c>
-      <c r="N19">
-        <f>M19/40</f>
+      <c r="N20">
+        <f>M20/40</f>
         <v>8.25</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="N20" t="s">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="N21">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N22">
         <f>8.25 * 2000</f>
         <v>16500</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="N22">
-        <f>N21/60</f>
-        <v>275</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N23">
         <f>N22/60</f>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N24">
+        <f>N23/60</f>
         <v>4.583333333333333</v>
       </c>
     </row>
@@ -6646,22 +6798,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>222</v>
+        <v>354</v>
       </c>
       <c r="D3">
-        <v>5410</v>
+        <v>9349</v>
       </c>
       <c r="E3">
-        <v>2086</v>
+        <v>3496</v>
       </c>
       <c r="F3">
-        <v>2595</v>
+        <v>4572</v>
       </c>
       <c r="G3">
-        <v>679</v>
+        <v>1195</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="I3" s="4" t="str">
         <f>B3</f>
@@ -6685,7 +6837,7 @@
       </c>
       <c r="N3">
         <f t="shared" ref="N3" si="3">1/G$3*G3</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
@@ -6693,22 +6845,22 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>227</v>
+        <v>354</v>
       </c>
       <c r="D4">
-        <v>5396</v>
+        <v>9324</v>
       </c>
       <c r="E4">
-        <v>2063</v>
+        <v>3506</v>
       </c>
       <c r="F4">
-        <v>2698</v>
+        <v>4668</v>
       </c>
       <c r="G4">
-        <v>635</v>
+        <v>1115</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I4" s="4" t="str">
         <f t="shared" ref="I4:I12" si="4">B4</f>
@@ -6716,47 +6868,47 @@
       </c>
       <c r="J4">
         <f t="shared" ref="J4:J12" si="5">1/C$3*C4</f>
-        <v>1.0225225225225225</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K12" si="6">1/D$3*D4</f>
-        <v>0.99741219963031424</v>
+        <v>0.99732591721039687</v>
       </c>
       <c r="L4">
         <f t="shared" ref="L4:L12" si="7">1/E$3*E4</f>
-        <v>0.98897411313518691</v>
+        <v>1.0028604118993134</v>
       </c>
       <c r="M4">
         <f t="shared" ref="M4:M12" si="8">1/F$3*F4</f>
-        <v>1.0396917148362235</v>
+        <v>1.0209973753280841</v>
       </c>
       <c r="N4">
         <f t="shared" ref="N4:N12" si="9">1/G$3*G4</f>
-        <v>0.93519882179675995</v>
+        <v>0.93305439330543927</v>
       </c>
       <c r="P4">
         <f>J4-J$3</f>
-        <v>2.2522522522522515E-2</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <f t="shared" ref="Q4:Q12" si="10">K4-K$3</f>
-        <v>-2.5878003696857554E-3</v>
+        <v>-2.6740827896031272E-3</v>
       </c>
       <c r="R4">
         <f t="shared" ref="R4:R12" si="11">L4-L$3</f>
-        <v>-1.1025886864813095E-2</v>
+        <v>2.8604118993134087E-3</v>
       </c>
       <c r="S4">
         <f t="shared" ref="S4:S12" si="12">M4-M$3</f>
-        <v>3.9691714836223468E-2</v>
+        <v>2.09973753280841E-2</v>
       </c>
       <c r="T4">
         <f t="shared" ref="T4:T12" si="13">N4-N$3</f>
-        <v>-6.4801178203240051E-2</v>
+        <v>-6.6945606694560622E-2</v>
       </c>
       <c r="U4">
         <f>SUM(P4:T4)</f>
-        <v>-1.6200628078992918E-2</v>
+        <v>-4.576190225676624E-2</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -6764,22 +6916,22 @@
         <v>23</v>
       </c>
       <c r="C5">
-        <v>252</v>
+        <v>381</v>
       </c>
       <c r="D5">
-        <v>6096</v>
+        <v>10311</v>
       </c>
       <c r="E5">
-        <v>2351</v>
+        <v>3808</v>
       </c>
       <c r="F5">
-        <v>3068</v>
+        <v>5252</v>
       </c>
       <c r="G5">
-        <v>674</v>
+        <v>1213</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="I5" s="4" t="str">
         <f t="shared" si="4"/>
@@ -6787,47 +6939,47 @@
       </c>
       <c r="J5">
         <f t="shared" si="5"/>
-        <v>1.1351351351351351</v>
+        <v>1.076271186440678</v>
       </c>
       <c r="K5">
         <f t="shared" si="6"/>
-        <v>1.1268022181146025</v>
+        <v>1.1028987057439299</v>
       </c>
       <c r="L5">
         <f t="shared" si="7"/>
-        <v>1.1270373921380632</v>
+        <v>1.0892448512585813</v>
       </c>
       <c r="M5">
         <f t="shared" si="8"/>
-        <v>1.1822736030828516</v>
+        <v>1.1487314085739282</v>
       </c>
       <c r="N5">
         <f t="shared" si="9"/>
-        <v>0.99263622974963184</v>
+        <v>1.0150627615062762</v>
       </c>
       <c r="P5">
         <f t="shared" ref="P5:P12" si="14">J5-J$3</f>
-        <v>0.13513513513513509</v>
+        <v>7.6271186440677985E-2</v>
       </c>
       <c r="Q5">
         <f t="shared" si="10"/>
-        <v>0.12680221811460246</v>
+        <v>0.1028987057439299</v>
       </c>
       <c r="R5">
         <f t="shared" si="11"/>
-        <v>0.1270373921380632</v>
+        <v>8.9244851258581281E-2</v>
       </c>
       <c r="S5">
         <f t="shared" si="12"/>
-        <v>0.18227360308285157</v>
+        <v>0.14873140857392819</v>
       </c>
       <c r="T5">
         <f t="shared" si="13"/>
-        <v>-7.3637702503681624E-3</v>
+        <v>1.5062761506276279E-2</v>
       </c>
       <c r="U5">
         <f t="shared" ref="U5:U12" si="15">SUM(P5:T5)</f>
-        <v>0.56388457822028415</v>
+        <v>0.43220891352339363</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -6835,22 +6987,22 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>283</v>
+        <v>433</v>
       </c>
       <c r="D6">
-        <v>6571</v>
+        <v>10997</v>
       </c>
       <c r="E6">
-        <v>2542</v>
+        <v>4114</v>
       </c>
       <c r="F6">
-        <v>3195</v>
+        <v>5416</v>
       </c>
       <c r="G6">
-        <v>833</v>
+        <v>1432</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I6" s="4" t="str">
         <f t="shared" si="4"/>
@@ -6858,47 +7010,47 @@
       </c>
       <c r="J6">
         <f t="shared" si="5"/>
-        <v>1.2747747747747749</v>
+        <v>1.2231638418079096</v>
       </c>
       <c r="K6">
         <f t="shared" si="6"/>
-        <v>1.2146025878003697</v>
+        <v>1.1762755374906408</v>
       </c>
       <c r="L6">
         <f t="shared" si="7"/>
-        <v>1.2186001917545541</v>
+        <v>1.1767734553775744</v>
       </c>
       <c r="M6">
         <f t="shared" si="8"/>
-        <v>1.23121387283237</v>
+        <v>1.1846019247594051</v>
       </c>
       <c r="N6">
         <f t="shared" si="9"/>
-        <v>1.2268041237113403</v>
+        <v>1.1983263598326359</v>
       </c>
       <c r="P6">
         <f t="shared" si="14"/>
-        <v>0.27477477477477485</v>
+        <v>0.2231638418079096</v>
       </c>
       <c r="Q6">
         <f t="shared" si="10"/>
-        <v>0.21460258780036967</v>
+        <v>0.17627553749064084</v>
       </c>
       <c r="R6">
         <f t="shared" si="11"/>
-        <v>0.21860019175455414</v>
+        <v>0.17677345537757438</v>
       </c>
       <c r="S6">
         <f t="shared" si="12"/>
-        <v>0.23121387283237005</v>
+        <v>0.18460192475940507</v>
       </c>
       <c r="T6">
         <f t="shared" si="13"/>
-        <v>0.22680412371134029</v>
+        <v>0.19832635983263602</v>
       </c>
       <c r="U6">
         <f t="shared" si="15"/>
-        <v>1.165995550873409</v>
+        <v>0.95914111926816592</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
@@ -6906,22 +7058,22 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>306</v>
+        <v>456</v>
       </c>
       <c r="D7">
-        <v>6726</v>
+        <v>10800</v>
       </c>
       <c r="E7">
-        <v>2734</v>
+        <v>4259</v>
       </c>
       <c r="F7">
-        <v>3028</v>
+        <v>4993</v>
       </c>
       <c r="G7">
-        <v>884</v>
+        <v>1432</v>
       </c>
       <c r="H7">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="I7" s="4" t="str">
         <f t="shared" si="4"/>
@@ -6929,47 +7081,47 @@
       </c>
       <c r="J7">
         <f t="shared" si="5"/>
-        <v>1.3783783783783783</v>
+        <v>1.2881355932203389</v>
       </c>
       <c r="K7">
         <f t="shared" si="6"/>
-        <v>1.2432532347504621</v>
+        <v>1.1552037651085678</v>
       </c>
       <c r="L7">
         <f t="shared" si="7"/>
-        <v>1.3106423777564717</v>
+        <v>1.2182494279176201</v>
       </c>
       <c r="M7">
         <f t="shared" si="8"/>
-        <v>1.166859344894027</v>
+        <v>1.0920822397200349</v>
       </c>
       <c r="N7">
         <f t="shared" si="9"/>
-        <v>1.3019145802650958</v>
+        <v>1.1983263598326359</v>
       </c>
       <c r="P7">
         <f t="shared" si="14"/>
-        <v>0.37837837837837829</v>
+        <v>0.28813559322033888</v>
       </c>
       <c r="Q7">
         <f t="shared" si="10"/>
-        <v>0.24325323475046212</v>
+        <v>0.15520376510856781</v>
       </c>
       <c r="R7">
         <f t="shared" si="11"/>
-        <v>0.31064237775647174</v>
+        <v>0.21824942791762014</v>
       </c>
       <c r="S7">
         <f t="shared" si="12"/>
-        <v>0.16685934489402698</v>
+        <v>9.2082239720034931E-2</v>
       </c>
       <c r="T7">
         <f t="shared" si="13"/>
-        <v>0.30191458026509577</v>
+        <v>0.19832635983263602</v>
       </c>
       <c r="U7">
         <f t="shared" si="15"/>
-        <v>1.4010479160444349</v>
+        <v>0.95199738579919779</v>
       </c>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.2">
@@ -6977,22 +7129,22 @@
         <v>19</v>
       </c>
       <c r="C8">
-        <v>277</v>
+        <v>436</v>
       </c>
       <c r="D8">
-        <v>6953</v>
+        <v>11901</v>
       </c>
       <c r="E8">
-        <v>2590</v>
+        <v>4717</v>
       </c>
       <c r="F8">
-        <v>3501</v>
+        <v>5676</v>
       </c>
       <c r="G8">
-        <v>865</v>
+        <v>1477</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I8" s="4" t="str">
         <f t="shared" si="4"/>
@@ -7000,47 +7152,47 @@
       </c>
       <c r="J8">
         <f t="shared" si="5"/>
-        <v>1.2477477477477477</v>
+        <v>1.231638418079096</v>
       </c>
       <c r="K8">
         <f t="shared" si="6"/>
-        <v>1.2852125693160812</v>
+        <v>1.2729703711626912</v>
       </c>
       <c r="L8">
         <f t="shared" si="7"/>
-        <v>1.2416107382550334</v>
+        <v>1.3492562929061784</v>
       </c>
       <c r="M8">
         <f t="shared" si="8"/>
-        <v>1.3491329479768785</v>
+        <v>1.2414698162729658</v>
       </c>
       <c r="N8">
         <f t="shared" si="9"/>
-        <v>1.2739322533136965</v>
+        <v>1.2359832635983263</v>
       </c>
       <c r="P8">
         <f t="shared" si="14"/>
-        <v>0.24774774774774766</v>
+        <v>0.23163841807909602</v>
       </c>
       <c r="Q8">
         <f t="shared" si="10"/>
-        <v>0.28521256931608119</v>
+        <v>0.27297037116269118</v>
       </c>
       <c r="R8">
         <f t="shared" si="11"/>
-        <v>0.24161073825503343</v>
+        <v>0.34925629290617843</v>
       </c>
       <c r="S8">
         <f t="shared" si="12"/>
-        <v>0.34913294797687855</v>
+        <v>0.24146981627296582</v>
       </c>
       <c r="T8">
         <f t="shared" si="13"/>
-        <v>0.27393225331369653</v>
+        <v>0.23598326359832644</v>
       </c>
       <c r="U8">
         <f t="shared" si="15"/>
-        <v>1.3976362566094374</v>
+        <v>1.331318162019258</v>
       </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.2">
@@ -7048,22 +7200,22 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>334</v>
+        <v>483</v>
       </c>
       <c r="D9" s="3">
-        <v>7037</v>
+        <v>11208</v>
       </c>
       <c r="E9">
-        <v>2764</v>
+        <v>4306</v>
       </c>
       <c r="F9">
-        <v>3217</v>
+        <v>5230</v>
       </c>
       <c r="G9">
-        <v>1020</v>
+        <v>1627</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="I9" s="4" t="str">
         <f t="shared" si="4"/>
@@ -7071,47 +7223,47 @@
       </c>
       <c r="J9">
         <f t="shared" si="5"/>
-        <v>1.5045045045045045</v>
+        <v>1.3644067796610169</v>
       </c>
       <c r="K9">
         <f t="shared" si="6"/>
-        <v>1.3007393715341959</v>
+        <v>1.1988447962348916</v>
       </c>
       <c r="L9">
         <f t="shared" si="7"/>
-        <v>1.3250239693192714</v>
+        <v>1.2316933638443937</v>
       </c>
       <c r="M9">
         <f t="shared" si="8"/>
-        <v>1.2396917148362234</v>
+        <v>1.1439195100612425</v>
       </c>
       <c r="N9">
         <f t="shared" si="9"/>
-        <v>1.5022091310751104</v>
+        <v>1.3615062761506276</v>
       </c>
       <c r="P9">
         <f t="shared" si="14"/>
-        <v>0.50450450450450446</v>
+        <v>0.36440677966101687</v>
       </c>
       <c r="Q9">
         <f t="shared" si="10"/>
-        <v>0.30073937153419594</v>
+        <v>0.1988447962348916</v>
       </c>
       <c r="R9">
         <f t="shared" si="11"/>
-        <v>0.32502396931927136</v>
+        <v>0.23169336384439365</v>
       </c>
       <c r="S9">
         <f t="shared" si="12"/>
-        <v>0.23969171483622342</v>
+        <v>0.14391951006124248</v>
       </c>
       <c r="T9">
         <f t="shared" si="13"/>
-        <v>0.50220913107511045</v>
+        <v>0.36150627615062769</v>
       </c>
       <c r="U9">
         <f t="shared" si="15"/>
-        <v>1.8721686912693056</v>
+        <v>1.3003707259521722</v>
       </c>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.2">
@@ -7119,22 +7271,22 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>306</v>
+        <v>455</v>
       </c>
       <c r="D10" s="3">
-        <v>7268</v>
+        <v>11821</v>
       </c>
       <c r="E10">
-        <v>2604</v>
+        <v>4186</v>
       </c>
       <c r="F10">
-        <v>3477</v>
+        <v>5709</v>
       </c>
       <c r="G10">
-        <v>1126</v>
+        <v>1830</v>
       </c>
       <c r="H10">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="I10" s="4" t="str">
         <f t="shared" si="4"/>
@@ -7142,47 +7294,47 @@
       </c>
       <c r="J10">
         <f t="shared" si="5"/>
-        <v>1.3783783783783783</v>
+        <v>1.2853107344632768</v>
       </c>
       <c r="K10">
         <f t="shared" si="6"/>
-        <v>1.3434380776340111</v>
+        <v>1.264413306235961</v>
       </c>
       <c r="L10">
         <f t="shared" si="7"/>
-        <v>1.2483221476510067</v>
+        <v>1.1973684210526316</v>
       </c>
       <c r="M10">
         <f t="shared" si="8"/>
-        <v>1.3398843930635838</v>
+        <v>1.2486876640419948</v>
       </c>
       <c r="N10">
         <f t="shared" si="9"/>
-        <v>1.6583210603829159</v>
+        <v>1.5313807531380752</v>
       </c>
       <c r="P10">
         <f t="shared" si="14"/>
-        <v>0.37837837837837829</v>
+        <v>0.28531073446327682</v>
       </c>
       <c r="Q10">
         <f t="shared" si="10"/>
-        <v>0.34343807763401113</v>
+        <v>0.26441330623596104</v>
       </c>
       <c r="R10">
         <f t="shared" si="11"/>
-        <v>0.24832214765100669</v>
+        <v>0.19736842105263164</v>
       </c>
       <c r="S10">
         <f t="shared" si="12"/>
-        <v>0.33988439306358376</v>
+        <v>0.24868766404199483</v>
       </c>
       <c r="T10">
         <f t="shared" si="13"/>
-        <v>0.65832106038291593</v>
+        <v>0.53138075313807531</v>
       </c>
       <c r="U10">
         <f t="shared" si="15"/>
-        <v>1.9683440571098958</v>
+        <v>1.5271608789319395</v>
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.2">
@@ -7190,22 +7342,22 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>278</v>
+        <v>430</v>
       </c>
       <c r="D11" s="3">
-        <v>7928</v>
+        <v>13126</v>
       </c>
       <c r="E11">
-        <v>3322</v>
+        <v>5449</v>
       </c>
       <c r="F11">
-        <v>3601</v>
+        <v>5960</v>
       </c>
       <c r="G11">
-        <v>1007</v>
+        <v>1685</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I11" s="4" t="str">
         <f t="shared" si="4"/>
@@ -7213,47 +7365,47 @@
       </c>
       <c r="J11">
         <f t="shared" si="5"/>
-        <v>1.2522522522522523</v>
+        <v>1.2146892655367232</v>
       </c>
       <c r="K11">
         <f t="shared" si="6"/>
-        <v>1.4654343807763401</v>
+        <v>1.4040004278532463</v>
       </c>
       <c r="L11">
         <f t="shared" si="7"/>
-        <v>1.592521572387344</v>
+        <v>1.5586384439359269</v>
       </c>
       <c r="M11">
         <f t="shared" si="8"/>
-        <v>1.3876685934489403</v>
+        <v>1.3035870516185477</v>
       </c>
       <c r="N11">
         <f t="shared" si="9"/>
-        <v>1.4830633284241532</v>
+        <v>1.4100418410041839</v>
       </c>
       <c r="P11">
         <f t="shared" si="14"/>
-        <v>0.25225225225225234</v>
+        <v>0.21468926553672318</v>
       </c>
       <c r="Q11">
         <f t="shared" si="10"/>
-        <v>0.46543438077634014</v>
+        <v>0.4040004278532463</v>
       </c>
       <c r="R11">
         <f t="shared" si="11"/>
-        <v>0.59252157238734404</v>
+        <v>0.55863844393592688</v>
       </c>
       <c r="S11">
         <f t="shared" si="12"/>
-        <v>0.38766859344894034</v>
+        <v>0.30358705161854771</v>
       </c>
       <c r="T11">
         <f t="shared" si="13"/>
-        <v>0.48306332842415323</v>
+        <v>0.41004184100418406</v>
       </c>
       <c r="U11">
         <f t="shared" si="15"/>
-        <v>2.1809401272890301</v>
+        <v>1.8909570299486282</v>
       </c>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.2">
@@ -7261,22 +7413,22 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>340</v>
+        <v>491</v>
       </c>
       <c r="D12" s="3">
-        <v>8314</v>
+        <v>12778</v>
       </c>
       <c r="E12">
-        <v>3311</v>
+        <v>4885</v>
       </c>
       <c r="F12">
-        <v>3693</v>
+        <v>5854</v>
       </c>
       <c r="G12">
-        <v>1245</v>
+        <v>1936</v>
       </c>
       <c r="H12">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="I12" s="4" t="str">
         <f t="shared" si="4"/>
@@ -7284,47 +7436,47 @@
       </c>
       <c r="J12">
         <f t="shared" si="5"/>
-        <v>1.5315315315315314</v>
+        <v>1.3870056497175141</v>
       </c>
       <c r="K12">
         <f t="shared" si="6"/>
-        <v>1.5367837338262476</v>
+        <v>1.3667771954219703</v>
       </c>
       <c r="L12">
         <f t="shared" si="7"/>
-        <v>1.587248322147651</v>
+        <v>1.3973112128146452</v>
       </c>
       <c r="M12">
         <f t="shared" si="8"/>
-        <v>1.4231213872832371</v>
+        <v>1.2804024496937882</v>
       </c>
       <c r="N12">
         <f t="shared" si="9"/>
-        <v>1.8335787923416789</v>
+        <v>1.6200836820083682</v>
       </c>
       <c r="P12">
         <f t="shared" si="14"/>
-        <v>0.53153153153153143</v>
+        <v>0.38700564971751406</v>
       </c>
       <c r="Q12">
         <f t="shared" si="10"/>
-        <v>0.53678373382624756</v>
+        <v>0.36677719542197029</v>
       </c>
       <c r="R12">
         <f t="shared" si="11"/>
-        <v>0.58724832214765099</v>
+        <v>0.39731121281464521</v>
       </c>
       <c r="S12">
         <f t="shared" si="12"/>
-        <v>0.42312138728323712</v>
+        <v>0.28040244969378825</v>
       </c>
       <c r="T12">
         <f t="shared" si="13"/>
-        <v>0.83357879234167886</v>
+        <v>0.62008368200836828</v>
       </c>
       <c r="U12">
         <f t="shared" si="15"/>
-        <v>2.9122637671303462</v>
+        <v>2.0515801896562862</v>
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.2">
@@ -7332,22 +7484,22 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>376</v>
+        <v>538</v>
       </c>
       <c r="D13" s="3">
-        <v>10209</v>
+        <v>15363</v>
       </c>
       <c r="E13">
-        <v>3526</v>
+        <v>5306</v>
       </c>
       <c r="F13">
-        <v>5011</v>
+        <v>7495</v>
       </c>
       <c r="G13">
-        <v>1663</v>
+        <v>2514</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="I13" s="4" t="str">
         <f t="shared" ref="I13" si="16">B13</f>
@@ -7355,23 +7507,23 @@
       </c>
       <c r="J13">
         <f t="shared" ref="J13" si="17">1/C$3*C13</f>
-        <v>1.6936936936936937</v>
+        <v>1.5197740112994351</v>
       </c>
       <c r="K13">
         <f t="shared" ref="K13" si="18">1/D$3*D13</f>
-        <v>1.8870609981515711</v>
+        <v>1.6432773558669378</v>
       </c>
       <c r="L13">
         <f t="shared" ref="L13" si="19">1/E$3*E13</f>
-        <v>1.6903163950143816</v>
+        <v>1.5177345537757436</v>
       </c>
       <c r="M13">
         <f t="shared" ref="M13" si="20">1/F$3*F13</f>
-        <v>1.9310211946050098</v>
+        <v>1.639326334208224</v>
       </c>
       <c r="N13">
         <f t="shared" ref="N13" si="21">1/G$3*G13</f>
-        <v>2.4491899852724592</v>
+        <v>2.1037656903765689</v>
       </c>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.2">
